--- a/templates/template-zone.xlsx
+++ b/templates/template-zone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/se140866/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\code\work\teacher-management\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B608D38-A3AD-414C-BAF8-FCC8AF07E553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080632E1-D8F1-4B9F-B3EE-1C8E34E210ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">    CÔNG TY CỔ PHẦN GIÁO DỤC</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Đánh giá</t>
-  </si>
-  <si>
-    <t>Cập nhật lúc: ....ngày:.../.../...</t>
   </si>
   <si>
     <t>TƯ VẤN</t>
@@ -132,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,7 +249,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -274,38 +271,35 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +542,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
+      <xdr:colOff>26670</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>195580</xdr:rowOff>
     </xdr:to>
@@ -836,63 +830,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" ht="26.1" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-    </row>
-    <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" ht="24" customHeight="1">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-    </row>
-    <row r="4" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="str">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="4" spans="1:14" ht="35.1" customHeight="1">
+      <c r="A4" s="12" t="str">
         <f>"KỲ THI ĐÁNH GIÁ HỌC KỲ II - NĂM HỌC: 2025 2026"&amp;CHAR(10)&amp;
 "BẢNG THỐNG KÊ KHU VỰC"&amp;CHAR(10)&amp;
 "TỈNH/THÀNH PHỐ: "&amp;data!B6&amp;CHAR(10)&amp;
@@ -902,112 +899,109 @@
 TỈNH/THÀNH PHỐ: Bình Dương
 CHƯƠNG TRÌNH GIÁO DỤC ICHI SKILL</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-    </row>
-    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" ht="21" customHeight="1">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" ht="21" customHeight="1">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" ht="35.1" customHeight="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" ht="29.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1028,61 +1022,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BEC2DD8-DFD8-CB40-BEE9-5FA61CF88304}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="30">
       <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="30">
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="30">
+      <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="30">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="13"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
